--- a/Workshop/Fabric PowerBI Capacity Planning Worksheet.xlsx
+++ b/Workshop/Fabric PowerBI Capacity Planning Worksheet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/38fedbb726841d9a/Packt/Workshop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/38fedbb726841d9a/Packt/Workshop/Materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C938CF22-E451-4603-B5A9-D19D8842CB1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{C938CF22-E451-4603-B5A9-D19D8842CB1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC6D1CF0-42F1-4DBE-9A7F-BCE36E46E886}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="-37640" yWindow="790" windowWidth="28800" windowHeight="15910" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,6 @@
     <sheet name="Summary" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1064,6 +1063,60 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>762000</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD37CFA5-F872-349F-C6A7-724476E68439}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="5270500" cy="6350000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1118,11 +1171,61 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>63500</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F871F2E-5E5C-D58F-B89B-E7D14F7FC561}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="5568950" cy="6350000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1490,7 +1593,7 @@
         <v>27</v>
       </c>
       <c r="B5" s="7">
-        <v>5.56</v>
+        <v>0.18</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>28</v>
@@ -2084,15 +2187,15 @@
       </c>
       <c r="G3" s="12">
         <f>B3*Inputs!$B$5</f>
-        <v>11.12</v>
+        <v>0.36</v>
       </c>
       <c r="H3" s="12">
         <f>G3*Inputs!$B$7*Inputs!$B$8</f>
-        <v>8006.4</v>
+        <v>259.20000000000005</v>
       </c>
       <c r="I3" s="12">
         <f>H3*(1-Inputs!$B$6)</f>
-        <v>4723.7760000000007</v>
+        <v>152.92800000000005</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>102</v>
@@ -2119,15 +2222,15 @@
       </c>
       <c r="G4" s="12">
         <f>B4*Inputs!$B$5</f>
-        <v>22.24</v>
+        <v>0.72</v>
       </c>
       <c r="H4" s="12">
         <f>G4*Inputs!$B$7*Inputs!$B$8</f>
-        <v>16012.8</v>
+        <v>518.40000000000009</v>
       </c>
       <c r="I4" s="12">
         <f>H4*(1-Inputs!$B$6)</f>
-        <v>9447.5520000000015</v>
+        <v>305.85600000000011</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>102</v>
@@ -2154,15 +2257,15 @@
       </c>
       <c r="G5" s="12">
         <f>B5*Inputs!$B$5</f>
-        <v>44.48</v>
+        <v>1.44</v>
       </c>
       <c r="H5" s="12">
         <f>G5*Inputs!$B$7*Inputs!$B$8</f>
-        <v>32025.599999999999</v>
+        <v>1036.8000000000002</v>
       </c>
       <c r="I5" s="12">
         <f>H5*(1-Inputs!$B$6)</f>
-        <v>18895.104000000003</v>
+        <v>611.71200000000022</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>102</v>
@@ -2189,15 +2292,15 @@
       </c>
       <c r="G6" s="12">
         <f>B6*Inputs!$B$5</f>
-        <v>88.96</v>
+        <v>2.88</v>
       </c>
       <c r="H6" s="12">
         <f>G6*Inputs!$B$7*Inputs!$B$8</f>
-        <v>64051.199999999997</v>
+        <v>2073.6000000000004</v>
       </c>
       <c r="I6" s="12">
         <f>H6*(1-Inputs!$B$6)</f>
-        <v>37790.208000000006</v>
+        <v>1223.4240000000004</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>102</v>
@@ -2224,15 +2327,15 @@
       </c>
       <c r="G7" s="12">
         <f>B7*Inputs!$B$5</f>
-        <v>177.92</v>
+        <v>5.76</v>
       </c>
       <c r="H7" s="12">
         <f>G7*Inputs!$B$7*Inputs!$B$8</f>
-        <v>128102.39999999999</v>
+        <v>4147.2000000000007</v>
       </c>
       <c r="I7" s="12">
         <f>H7*(1-Inputs!$B$6)</f>
-        <v>75580.416000000012</v>
+        <v>2446.8480000000009</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>102</v>
@@ -2259,15 +2362,15 @@
       </c>
       <c r="G8" s="12">
         <f>B8*Inputs!$B$5</f>
-        <v>355.84</v>
+        <v>11.52</v>
       </c>
       <c r="H8" s="12">
         <f>G8*Inputs!$B$7*Inputs!$B$8</f>
-        <v>256204.79999999999</v>
+        <v>8294.4000000000015</v>
       </c>
       <c r="I8" s="12">
         <f>H8*(1-Inputs!$B$6)</f>
-        <v>151160.83200000002</v>
+        <v>4893.6960000000017</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>102</v>
@@ -2294,15 +2397,15 @@
       </c>
       <c r="G9" s="12">
         <f>B9*Inputs!$B$5</f>
-        <v>711.68</v>
+        <v>23.04</v>
       </c>
       <c r="H9" s="12">
         <f>G9*Inputs!$B$7*Inputs!$B$8</f>
-        <v>512409.59999999998</v>
+        <v>16588.800000000003</v>
       </c>
       <c r="I9" s="12">
         <f>H9*(1-Inputs!$B$6)</f>
-        <v>302321.66400000005</v>
+        <v>9787.3920000000035</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>102</v>
@@ -2329,15 +2432,15 @@
       </c>
       <c r="G10" s="12">
         <f>B10*Inputs!$B$5</f>
-        <v>1423.36</v>
+        <v>46.08</v>
       </c>
       <c r="H10" s="12">
         <f>G10*Inputs!$B$7*Inputs!$B$8</f>
-        <v>1024819.2</v>
+        <v>33177.600000000006</v>
       </c>
       <c r="I10" s="12">
         <f>H10*(1-Inputs!$B$6)</f>
-        <v>604643.3280000001</v>
+        <v>19574.784000000007</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>102</v>
@@ -2364,15 +2467,15 @@
       </c>
       <c r="G11" s="12">
         <f>B11*Inputs!$B$5</f>
-        <v>2846.72</v>
+        <v>92.16</v>
       </c>
       <c r="H11" s="12">
         <f>G11*Inputs!$B$7*Inputs!$B$8</f>
-        <v>2049638.3999999999</v>
+        <v>66355.200000000012</v>
       </c>
       <c r="I11" s="12">
         <f>H11*(1-Inputs!$B$6)</f>
-        <v>1209286.6560000002</v>
+        <v>39149.568000000014</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>102</v>
@@ -2399,15 +2502,15 @@
       </c>
       <c r="G12" s="12">
         <f>B12*Inputs!$B$5</f>
-        <v>5693.44</v>
+        <v>184.32</v>
       </c>
       <c r="H12" s="12">
         <f>G12*Inputs!$B$7*Inputs!$B$8</f>
-        <v>4099276.7999999998</v>
+        <v>132710.40000000002</v>
       </c>
       <c r="I12" s="12">
         <f>H12*(1-Inputs!$B$6)</f>
-        <v>2418573.3120000004</v>
+        <v>78299.136000000028</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>102</v>
@@ -2434,15 +2537,15 @@
       </c>
       <c r="G13" s="12">
         <f>B13*Inputs!$B$5</f>
-        <v>11386.88</v>
+        <v>368.64</v>
       </c>
       <c r="H13" s="12">
         <f>G13*Inputs!$B$7*Inputs!$B$8</f>
-        <v>8198553.5999999996</v>
+        <v>265420.80000000005</v>
       </c>
       <c r="I13" s="12">
         <f>H13*(1-Inputs!$B$6)</f>
-        <v>4837146.6240000008</v>
+        <v>156598.27200000006</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>102</v>
@@ -3003,11 +3106,11 @@
       </c>
       <c r="C5" s="12">
         <f>VLOOKUP(C3,'SKU Catalog'!$A$3:$I$13,8,FALSE)</f>
-        <v>128102.39999999999</v>
+        <v>4147.2000000000007</v>
       </c>
       <c r="D5" s="12">
         <f>VLOOKUP(D3,'SKU Catalog'!$A$3:$I$13,8,FALSE)</f>
-        <v>256204.79999999999</v>
+        <v>8294.4000000000015</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>163</v>
@@ -3035,11 +3138,11 @@
       </c>
       <c r="C6" s="12">
         <f>VLOOKUP(C3,'SKU Catalog'!$A$3:$I$13,9,FALSE)</f>
-        <v>75580.416000000012</v>
+        <v>2446.8480000000009</v>
       </c>
       <c r="D6" s="12">
         <f>VLOOKUP(D3,'SKU Catalog'!$A$3:$I$13,9,FALSE)</f>
-        <v>151160.83200000002</v>
+        <v>4893.6960000000017</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>163</v>
@@ -3323,11 +3426,11 @@
       </c>
       <c r="C15" s="12">
         <f>SUM(C5,C10:C14)</f>
-        <v>133707.4</v>
+        <v>9752.2000000000007</v>
       </c>
       <c r="D15" s="12">
         <f>SUM(D5,D10:D14)</f>
-        <v>257609.8</v>
+        <v>9699.4000000000015</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>163</v>
@@ -3355,11 +3458,11 @@
       </c>
       <c r="C16" s="12">
         <f>SUM(C6,C10:C14)</f>
-        <v>81185.416000000012</v>
+        <v>8051.8480000000009</v>
       </c>
       <c r="D16" s="12">
         <f>SUM(D6,D10:D14)</f>
-        <v>152565.83200000002</v>
+        <v>6298.6960000000017</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>163</v>
@@ -3495,7 +3598,7 @@
       </c>
       <c r="B7" s="12">
         <f>VLOOKUP(B6,'SKU Catalog'!$A$3:$I$13,8,FALSE)</f>
-        <v>512409.59999999998</v>
+        <v>16588.800000000003</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>163</v>
@@ -3516,7 +3619,7 @@
       </c>
       <c r="B8" s="12">
         <f>VLOOKUP(B6,'SKU Catalog'!$A$3:$I$13,9,FALSE)</f>
-        <v>302321.66400000005</v>
+        <v>9787.3920000000035</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>163</v>
@@ -3537,7 +3640,7 @@
       </c>
       <c r="B9" s="12">
         <f>Scenarios!C15</f>
-        <v>133707.4</v>
+        <v>9752.2000000000007</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>163</v>
@@ -3558,7 +3661,7 @@
       </c>
       <c r="B10" s="12">
         <f>Scenarios!D15</f>
-        <v>257609.8</v>
+        <v>9699.4000000000015</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>163</v>
@@ -3579,7 +3682,7 @@
       </c>
       <c r="B11" s="12">
         <f>Scenarios!C16</f>
-        <v>81185.416000000012</v>
+        <v>8051.8480000000009</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>163</v>
@@ -3600,7 +3703,7 @@
       </c>
       <c r="B12" s="12">
         <f>Scenarios!D16</f>
-        <v>152565.83200000002</v>
+        <v>6298.6960000000017</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>163</v>
@@ -3697,11 +3800,11 @@
       </c>
       <c r="B18" s="18">
         <f>Scenarios!C15</f>
-        <v>133707.4</v>
+        <v>9752.2000000000007</v>
       </c>
       <c r="C18" s="18">
         <f>Scenarios!C16</f>
-        <v>81185.416000000012</v>
+        <v>8051.8480000000009</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
@@ -3717,11 +3820,11 @@
       </c>
       <c r="B19" s="18">
         <f>Scenarios!D15</f>
-        <v>257609.8</v>
+        <v>9699.4000000000015</v>
       </c>
       <c r="C19" s="18">
         <f>Scenarios!D16</f>
-        <v>152565.83200000002</v>
+        <v>6298.6960000000017</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
